--- a/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Ibrahim se lève. Le tapis est doux. Papa l'appelle. Papa est dans la salle de bain. L'eau coule. Ibrahim prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ibrahim rit un peu. Il crache dans le lavabo. Il se rince. Le soir, c'est pareil. Ibrahim prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble. Ibrahim dit : matin et soir. Papa dit : oui, avec moi. Les dents sont propres. Ibrahim range la brosse.</t>
+          <t>C'est le matin. Ibrahim se lève. Le tapis est doux. Papa l'appelle. Papa est dans la salle de bain. L'eau coule. Ibrahim prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ibrahim rit un peu. Il crache dans le lavabo. Il se rince. Le soir, c'est pareil. Ibrahim prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble. Matin et soir. Oui, avec moi. Les dents sont propres. Ibrahim range la brosse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Ibrahim se lève. Le tapis est doux. Papa l'appelle. Papa est dans la salle de bain. L'eau coule. Ibrahim prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ibrahim rit un peu. Il crache dans le lavabo. Il se rince. Le soir, c'est pareil. Ibrahim prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble.
+enfant-m|Matin et soir.
+papa|Oui, avec moi.
+narrateur|Les dents sont propres. Ibrahim range la brosse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ibrahim se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ibrahim a pris la brosse. Il brosse avec l'adulte. C'est papa. Matin et soir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ibrahim se rince la bouche. Il dit merci à papa. Les dents brillent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 narrateur|Les dents sont propres. Ibrahim range la brosse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Ibrahim se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Ibrahim a pris la brosse. Il brosse avec l'adulte. C'est papa. Matin et soir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Ibrahim se rince la bouche. Il dit merci à papa. Les dents brillent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La brosse d'Ibrahim</t>
+          <t>Le rideau aux poissons d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le rideau aux poissons bouge. Amir prend sa brosse avec papa, le matin puis le soir. Le tapis est doux. Les dents brillent.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Ibrahim se lève. Le tapis est doux. Papa l'appelle. Papa est dans la salle de bain. L'eau coule. Ibrahim prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ibrahim rit un peu. Il crache dans le lavabo. Il se rince. Le soir, c'est pareil. Ibrahim prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble. Matin et soir. Oui, avec moi. Les dents sont propres. Ibrahim range la brosse.</t>
+          <t>Le rideau aux poissons bouge un peu. Une goutte tombe du robinet. Le tapis de bain est tout doux. Un gobelet bleu attend près de l'eau. Ça sent le savon, tout léger. Un poisson du rideau est jaune. Amir, viens. L'eau coule. J'arrive, papa. Tu vois le poisson jaune ? Oui. Sur le rideau. En ce moment, Amir se lève. Le tapis est doux sous ses pieds. Papa est dans la salle de bain. L'eau coule. Prends ta brosse. Ma brosse. Amir prend sa brosse. Papa prend la sienne. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ça chatouille. Oui. On brosse ensemble. Amir rit un peu. Il se rince. Il range la brosse. Bravo. Tu as fait du bon travail. C'est le matin. On a brossé. Avec toi. Oui. Avec un adulte. Plus tard, le soir arrive. Le rideau aux poissons bouge encore. La goutte fait encore ploc. Amir, viens. C'est le soir. Ma brosse. Amir prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec moi. Avec un adulte. Les dents sont propres. Amir range la brosse. Tu as fini de brosser ? Oui, papa. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,60 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Ibrahim se lève. Le tapis est doux. Papa l'appelle. Papa est dans la salle de bain. L'eau coule. Ibrahim prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ibrahim rit un peu. Il crache dans le lavabo. Il se rince. Le soir, c'est pareil. Ibrahim prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble.
+          <t>narrateur|Le rideau aux poissons bouge un peu.
+narrateur|Une goutte tombe du robinet.
+narrateur|Le tapis de bain est tout doux.
+narrateur|Un gobelet bleu attend près de l'eau.
+narrateur|Ça sent le savon, tout léger.
+narrateur|Un poisson du rideau est jaune.
+papa|Amir, viens. L'eau coule.
+enfant-m|J'arrive, papa.
+papa|Tu vois le poisson jaune ?
+enfant-m|Oui. Sur le rideau.
+narrateur|En ce moment, Amir se lève.
+narrateur|Le tapis est doux sous ses pieds.
+narrateur|Papa est dans la salle de bain.
+narrateur|L'eau coule.
+papa|Prends ta brosse.
+enfant-m|Ma brosse.
+narrateur|Amir prend sa brosse.
+narrateur|Papa prend la sienne.
+narrateur|Un adulte est avec lui.
+narrateur|C'est papa.
+narrateur|Ils se brossent les dents.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
+narrateur|L'eau est fraîche.
+enfant-m|Ça chatouille.
+papa|Oui. On brosse ensemble.
+narrateur|Amir rit un peu.
+narrateur|Il se rince.
+narrateur|Il range la brosse.
+papa|Bravo. Tu as fait du bon travail.
+papa|C'est le matin. On a brossé.
+enfant-m|Avec toi.
+papa|Oui. Avec un adulte.
+narrateur|Plus tard, le soir arrive.
+narrateur|Le rideau aux poissons bouge encore.
+narrateur|La goutte fait encore ploc.
+papa|Amir, viens. C'est le soir.
+enfant-m|Ma brosse.
+narrateur|Amir prend sa brosse.
+narrateur|Un adulte est avec lui.
+narrateur|C'est papa.
+narrateur|Ils brossent ensemble.
+narrateur|La brosse va en haut.
+narrateur|La brosse va en bas.
 enfant-m|Matin et soir.
 papa|Oui, avec moi.
-narrateur|Les dents sont propres. Ibrahim range la brosse.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Avec un adulte.
+narrateur|Les dents sont propres.
+narrateur|Amir range la brosse.
+papa|Tu as fini de brosser ?
+enfant-m|Oui, papa.
+papa|Bravo, Amir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,7 +1402,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ibrahim se brosse les dents. Avec quoi ?</t>
+          <t>Amir se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,10 +1562,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ibrahim se brosse les dents. Avec quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir se brosse les dents.
+narrateur|Avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ibrahim a pris la brosse. Il brosse avec l'adulte. C'est papa. Matin et soir.</t>
+          <t>Amir a pris la brosse. Il brosse avec l'adulte. C'est papa. Matin et soir. Tu te souviens ? Matin et soir. Oui. Avec papa. Bravo. C'est le bon geste. Le tapis est encore doux. Le gobelet bleu attend. Le poisson jaune ne bouge plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,10 +1734,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ibrahim a pris la brosse. Il brosse avec l'adulte. C'est papa. Matin et soir.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a pris la brosse.
+narrateur|Il brosse avec l'adulte.
+narrateur|C'est papa.
+narrateur|Matin et soir.
+papa|Tu te souviens ? Matin et soir.
+enfant-m|Oui. Avec papa.
+papa|Bravo. C'est le bon geste.
+narrateur|Le tapis est encore doux.
+narrateur|Le gobelet bleu attend.
+narrateur|Le poisson jaune ne bouge plus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ibrahim se rince la bouche. Il dit merci à papa. Les dents brillent.</t>
+          <t>Amir se rince la bouche. L'eau est fraîche. Merci, papa. Tes dents brillent. Tu as fini ? Oui. Bravo. On va au lit. Le rideau aux poissons s'arrête. Le tapis reste doux. Le gobelet bleu reste près de l'eau.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,10 +1906,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ibrahim se rince la bouche. Il dit merci à papa. Les dents brillent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Amir se rince la bouche.
+narrateur|L'eau est fraîche.
+enfant-m|Merci, papa.
+papa|Tes dents brillent.
+papa|Tu as fini ?
+enfant-m|Oui.
+papa|Bravo. On va au lit.
+narrateur|Le rideau aux poissons s'arrête.
+narrateur|Le tapis reste doux.
+narrateur|Le gobelet bleu reste près de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,7 +1942,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir a brossé le matin. Amir a brossé le soir. Avec papa. Avec la brosse. Bravo, Amir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,10 +2082,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Amir a brossé le matin.
+narrateur|Amir a brossé le soir.
+narrateur|Avec papa. Avec la brosse.
+papa|Bravo, Amir.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le rideau aux poissons bouge un peu. Une goutte tombe du robinet. Le tapis de bain est tout doux. Un gobelet bleu attend près de l'eau. Ça sent le savon, tout léger. Un poisson du rideau est jaune. Amir, viens. L'eau coule. J'arrive, papa. Tu vois le poisson jaune ? Oui. Sur le rideau. En ce moment, Amir se lève. Le tapis est doux sous ses pieds. Papa est dans la salle de bain. L'eau coule. Prends ta brosse. Ma brosse. Amir prend sa brosse. Papa prend la sienne. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ça chatouille. Oui. On brosse ensemble. Amir rit un peu. Il se rince. Il range la brosse. Bravo. Tu as fait du bon travail. C'est le matin. On a brossé. Avec toi. Oui. Avec un adulte. Plus tard, le soir arrive. Le rideau aux poissons bouge encore. La goutte fait encore ploc. Amir, viens. C'est le soir. Ma brosse. Amir prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec moi. Avec un adulte. Les dents sont propres. Amir range la brosse. Tu as fini de brosser ? Oui, papa. Bravo, Amir.</t>
+          <t>Le rideau aux poissons bouge un peu. Une goutte tombe du robinet. Le tapis de bain est tout doux. Un gobelet bleu attend près de l'eau. Ça sent le savon, tout léger. Un poisson du rideau est jaune. Amir, viens. L'eau coule. J'arrive, papa. Tu vois le poisson jaune ? Oui. Sur le rideau. En ce moment, Amir se lève. Le tapis est doux sous ses pieds. Papa est dans la salle de bain. L'eau coule. Prends ta brosse. Ma brosse. Amir prend sa brosse. Papa prend la sienne. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ça chatouille. Oui. On brosse ensemble. Amir rit un peu. Il se rince. Il range la brosse. Le matin, on a brossé. Avec toi. Oui. Avec un adulte. Amir regarde le poisson jaune. Le tapis est encore doux. Il est doux, papa. Oui. Bravo. Plus tard, le soir arrive. Le rideau aux poissons bouge encore. La goutte fait encore ploc. Amir, viens. C'est le soir. Ma brosse. Amir prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec moi. Avec un adulte. Les dents sont propres. Amir range la brosse. Tu as fini de brosser ? Oui, papa. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est le &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt;. Ibrahim se lève. Le tapis est doux. Papa l'appelle. Papa est dans la salle de bain. L'eau coule. Ibrahim prend sa brosse. Papa prend la sienne. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ibrahim rit un peu. Il crache dans le lavabo. Il se rince. Le soir, c'est pareil. Ibrahim prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble. Ibrahim dit : matin et soir. Papa dit : oui, avec moi. Les dents sont propres. Ibrahim range la brosse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau aux poissons bouge un peu. Une goutte tombe du robinet. Le tapis de bain est tout doux. Un gobelet bleu attend près de l'eau. Ça sent le savon, tout léger. Un poisson du rideau est jaune. Amir, viens. L'eau coule. J'arrive, papa. Tu vois le poisson jaune ? Oui. Sur le rideau. En ce moment, Amir se lève. Le tapis est doux sous ses pieds. Papa est dans la salle de bain. L'eau coule. Prends ta brosse. Ma brosse. Amir prend sa brosse. Papa prend la sienne. Un adulte est avec lui. C'est papa. Ils se brossent les dents. La brosse va en haut. La brosse va en bas. L'eau est fraîche. Ça chatouille. Oui. On brosse ensemble. Amir rit un peu. Il se rince. Il range la brosse. Le matin, on a brossé. Avec toi. Oui. Avec un adulte. Amir regarde le poisson jaune. Le tapis est encore doux. Il est doux, papa. Oui. Bravo. Plus tard, le soir arrive. Le rideau aux poissons bouge encore. La goutte fait encore ploc. Amir, viens. C'est le soir. Ma brosse. Amir prend sa brosse. Un adulte est avec lui. C'est papa. Ils brossent ensemble. La brosse va en haut. La brosse va en bas. Matin et soir. Oui, avec moi. Avec un adulte. Les dents sont propres. Amir range la brosse. Tu as fini de brosser ? Oui, papa. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1353,10 +1353,13 @@
 narrateur|Amir rit un peu.
 narrateur|Il se rince.
 narrateur|Il range la brosse.
-papa|Bravo. Tu as fait du bon travail.
-papa|C'est le matin. On a brossé.
+papa|Le matin, on a brossé.
 enfant-m|Avec toi.
 papa|Oui. Avec un adulte.
+narrateur|Amir regarde le poisson jaune.
+narrateur|Le tapis est encore doux.
+enfant-m|Il est doux, papa.
+papa|Oui. Bravo.
 narrateur|Plus tard, le soir arrive.
 narrateur|Le rideau aux poissons bouge encore.
 narrateur|La goutte fait encore ploc.
@@ -1407,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ibrahim se &lt;emphasis level="moderate"&gt;brosse&lt;/emphasis&gt; les dents. Avec quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir se brosse les dents. Avec quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,7 +1598,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ibrahim a pris la brosse. Il brosse avec l'adulte. C'est papa. &lt;emphasis level="moderate"&gt;matin&lt;/emphasis&gt; et soir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a pris la brosse. Il brosse avec l'adulte. C'est papa. Matin et soir. Tu te souviens ? Matin et soir. Oui. Avec papa. Bravo. C'est le bon geste. Le tapis est encore doux. Le gobelet bleu attend. Le poisson jaune ne bouge plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1775,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ibrahim se rince la bouche. Il dit merci à papa. Les dents brillent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir se rince la bouche. L'eau est fraîche. Merci, papa. Tes dents brillent. Tu as fini ? Oui. Bravo. On va au lit. Le rideau aux poissons s'arrête. Le tapis reste doux. Le gobelet bleu reste près de l'eau.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Amir a brossé le matin. Amir a brossé le soir. Avec papa. Avec la brosse. Bravo, Amir. L'histoire est finie.</t>
+          <t>Amir a brossé le matin. Amir a brossé le soir. Avec papa. Avec la brosse. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a brossé le matin. Amir a brossé le soir. Avec papa. Avec la brosse. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2085,8 +2088,7 @@
           <t>narrateur|Amir a brossé le matin.
 narrateur|Amir a brossé le soir.
 narrateur|Avec papa. Avec la brosse.
-papa|Bravo, Amir.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Amir.</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2152,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.002-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ibrahim, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
